--- a/Grade-6_Week-03_2026-09-28--2026-10-02_English_Revision-Part-2/Grade-6_Week-03_English_Lesson-Plan.xlsx
+++ b/Grade-6_Week-03_2026-09-28--2026-10-02_English_Revision-Part-2/Grade-6_Week-03_English_Lesson-Plan.xlsx
@@ -716,7 +716,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Prepared by Ogün Aydın · CC BY 4.0: free to use, share and adapt with credit · codeberg.org/helinesca/ingilizce-6-materyaller</t>
+          <t>Prepared by Ogün Aydın · CC BY 4.0: free to use, share and adapt with credit · github.com/ogunaydin89/ingilizce-6-materyaller</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Prepared by Ogün Aydın · CC BY 4.0: free to use, share and adapt with credit · codeberg.org/helinesca/ingilizce-6-materyaller</oddFooter>
+    <oddFooter>&amp;C&amp;7 Prepared by Ogün Aydın · CC BY 4.0: free to use, share and adapt with credit · github.com/ogunaydin89/ingilizce-6-materyaller</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
